--- a/resources/class06/review-func-dep.xlsx
+++ b/resources/class06/review-func-dep.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jmac\Google Drive\courses\databases\lectures\06-er-to-relational\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C1B5217-60AF-4244-9ECA-0B2DD8DB18B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{4F93D798-FE40-FC4E-8F57-2D23E776851F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{039E0953-FCC1-4693-9C45-823DCDC47526}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{039E0953-FCC1-4693-9C45-823DCDC47526}"/>
   </bookViews>
   <sheets>
     <sheet name="unnormalized" sheetId="1" r:id="rId1"/>
     <sheet name="normalized" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,6 +28,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -241,9 +243,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -281,7 +283,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -387,7 +389,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -529,7 +531,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -538,21 +540,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA6DFB72-656B-4121-9166-B3C5B62CA56F}">
   <dimension ref="B2:F17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="15.28515625" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="33.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" customWidth="1"/>
+    <col min="3" max="3" width="17.75390625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.234375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.3125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.62890625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" ht="29.25" x14ac:dyDescent="0.4">
       <c r="B2" s="9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:6" ht="27.75" x14ac:dyDescent="0.2">
       <c r="B4" s="4" t="s">
         <v>18</v>
       </c>
@@ -569,7 +571,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B5" s="2">
         <v>6</v>
       </c>
@@ -586,7 +588,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B6" s="2">
         <v>18</v>
       </c>
@@ -603,7 +605,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B7" s="2">
         <v>8</v>
       </c>
@@ -620,7 +622,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B8" s="2">
         <v>18</v>
       </c>
@@ -637,7 +639,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>8</v>
       </c>
@@ -654,7 +656,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>11</v>
       </c>
@@ -671,7 +673,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B11" s="2">
         <v>23</v>
       </c>
@@ -688,30 +690,30 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B13" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B15" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B17" s="1" t="s">
         <v>25</v>
       </c>
@@ -725,21 +727,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0413B5A0-72F5-4173-AE1D-D2B15C2768FD}">
   <dimension ref="B2:F22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="13.85546875" customWidth="1"/>
-    <col min="3" max="3" width="22.28515625" customWidth="1"/>
-    <col min="4" max="4" width="33" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" customWidth="1"/>
-    <col min="6" max="6" width="33" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.328125" customWidth="1"/>
+    <col min="4" max="4" width="32.95703125" customWidth="1"/>
+    <col min="5" max="5" width="18.6953125" customWidth="1"/>
+    <col min="6" max="6" width="32.95703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:6" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B2" s="8" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:6" ht="27.75" x14ac:dyDescent="0.2">
       <c r="B4" s="4" t="s">
         <v>18</v>
       </c>
@@ -752,7 +754,7 @@
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B5" s="2">
         <v>6</v>
       </c>
@@ -765,7 +767,7 @@
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B6" s="2">
         <v>18</v>
       </c>
@@ -778,7 +780,7 @@
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B7" s="2">
         <v>8</v>
       </c>
@@ -791,7 +793,7 @@
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B8" s="2">
         <v>18</v>
       </c>
@@ -804,7 +806,7 @@
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>8</v>
       </c>
@@ -817,7 +819,7 @@
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>11</v>
       </c>
@@ -830,7 +832,7 @@
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B11" s="2">
         <v>23</v>
       </c>
@@ -843,7 +845,7 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
     </row>
-    <row r="14" spans="2:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:6" ht="27.75" x14ac:dyDescent="0.2">
       <c r="B14" s="4" t="s">
         <v>20</v>
       </c>
@@ -854,7 +856,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B15" s="3" t="s">
         <v>0</v>
       </c>
@@ -865,7 +867,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B16" s="3" t="s">
         <v>2</v>
       </c>
@@ -876,38 +878,38 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B19" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B20" s="7" t="s">
         <v>26</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B21" s="7" t="s">
         <v>27</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B22" s="7" t="s">
         <v>29</v>
       </c>
